--- a/cosco-shipping/数据源/中远海控_财报核心数据.xlsx
+++ b/cosco-shipping/数据源/中远海控_财报核心数据.xlsx
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1519,6 +1519,37 @@
         <v>11.35</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>601.25</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1119.22</v>
+      </c>
+      <c r="D23" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="E23" t="n">
+        <v>75.42</v>
+      </c>
+      <c r="F23" t="n">
+        <v>134.19</v>
+      </c>
+      <c r="G23" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>75.27</v>
+      </c>
+      <c r="J23" t="n">
+        <v>12.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1530,7 +1561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1732,6 +1763,36 @@
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>中报10派5.6元 + 年报10派4.4元（2026-03预案，2026-05实施）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026年</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E7" t="n">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>134.19</v>
+      </c>
+      <c r="G7" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>中期分红每股0.43元（含税，占H1归母49%）；全年分红待2026年报</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2309,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>年度: 2021-2025 年报; 季度: 2021Q1 - 2026Q1 一季报</t>
+          <t>年度: 2021-2025 年报; 季度: 2021Q1 - 2026Q2 中报（累计口径，单季为 H1−Q1 推算）</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2664,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>- 经营现金流/资产负债率/ROE/EPS 多为年度或期末指标; 季度表仅 2026Q1 列示其一季报值, 其余季度留空。</t>
+          <t>2026Q1 列示一季报值、2026Q2 列示中报值（单季财务/箱量=H1−Q1 推算，非公司单季披露）；其余季度留空。</t>
         </is>
       </c>
       <c r="B39" s="6" t="n"/>
